--- a/marketer_forms/021_marketing_quote_form--marketer_forms.xlsx
+++ b/marketer_forms/021_marketing_quote_form--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>service_type</t>
+          <t>Service Type</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -594,14 +594,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>client_name</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
           <t>Client Name</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -621,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>client_email</t>
+          <t>Client Email</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -644,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>client_phone</t>
+          <t>Client Phone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -680,24 +676,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>marketing_quote_form_service_type</t>
+          <t>marketing_quote_form_quote</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>service_type</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Select a service type</t>
-        </is>
-      </c>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -707,24 +699,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>marketing_quote_form_service_details</t>
+          <t>marketing_quote_form_terms_and_conditions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>service_details</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Service details</t>
-        </is>
-      </c>
+          <t>Terms and Conditions</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -734,24 +722,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>marketing_quote_form_quote</t>
+          <t>marketing_quote_form_submit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>quote</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Enter a quote</t>
-        </is>
-      </c>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -761,24 +745,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>marketing_quote_form_terms_and_conditions</t>
+          <t>marketing_quote_form_agreed_by</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>terms_and_conditions</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Accept terms and conditions to proceed</t>
-        </is>
-      </c>
+          <t>Agreed by</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -788,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>marketing_quote_form_submit</t>
+          <t>marketing_quote_form_agreed_on</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Agreed on</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -811,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>marketing_quote_form_additional_info</t>
+          <t>marketing_quote_form_service_price</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>additional_info</t>
+          <t>Service Price</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>marketing_quote_form_service_agreed</t>
+          <t>marketing_quote_form_agreed_price</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>service_agreed</t>
+          <t>Agreed Price</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -857,271 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>marketing_quote_form_quote_agreed</t>
+          <t>marketing_quote_form_price_valid_until</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>quote_agreed</t>
+          <t>Price Valid until</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>marketing_quote_form_agreed_by</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>agreed_by</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Agreed by</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>marketing_quote_form_agreed_on</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>agreed_on</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Date of agreement</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>marketing_quote_form_service_price</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Enter service price</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>marketing_quote_form_agreed_price</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>agreed_price</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Agreed price</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>marketing_quote_form_agreed_price_valid_until</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>agreed_price_valid_until</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Price valid until</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>marketing_quote_form_service_agreed</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>service_agreed</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>marketing_quote_form_quote_agreed</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>quote_agreed</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>marketing_quote_form_agreed_by</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>agreed_by</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>marketing_quote_form_agreed_on</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>agreed_on</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>marketing_quote_form_agreed_price_valid</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>agreed_price_valid</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1138,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1171,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>marketing_agency</t>
+          <t>digital_marketing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Marketing Agency</t>
+          <t>Digital Marketing</t>
         </is>
       </c>
     </row>
@@ -1188,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>freelancer</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Freelancer</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1205,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>consultant</t>
+          <t>content_creation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Content Creation</t>
         </is>
       </c>
     </row>
@@ -1222,95 +952,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>digital_marketing</t>
+          <t>branding</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Digital Marketing</t>
+          <t>Branding</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>marketing_quote_form_service_type_choices</t>
+          <t>marketing_quote_form_submit_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>submit_form</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Social Media</t>
+          <t>Submit Form</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>marketing_quote_form_service_type_choices</t>
+          <t>marketing_quote_form_submit_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>content_creation</t>
+          <t>cancel_form</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>Content Creation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>marketing_quote_form_service_type_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>branding</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Branding</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>marketing_quote_form_submit_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>submit_form</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Submit Form</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>marketing_quote_form_submit_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>cancel_form</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>Cancel Form</t>
         </is>
